--- a/backend/planos_unoee/ARCHIVO PLANO TNL-VACACIONES.xlsx
+++ b/backend/planos_unoee/ARCHIVO PLANO TNL-VACACIONES.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gyj365-my.sharepoint.com/personal/soporte_aplicaciones_gyj_com_co/Documents/informacion/Documentos/documentos TIC/rhh/vacaciones colectivas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\proyectos gyj\vacaccionesGyJ-V2\backend\planos_unoee\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{007BD98E-D647-4E0D-A475-B98E530A3D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A3ACFFDF-C84A-4BBD-B107-BBF23B430779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
   <si>
     <t>EMPRESA (Obligatorio)</t>
   </si>
@@ -115,12 +115,6 @@
   </si>
   <si>
     <t>ENTIDAD EPS O ARL (  No obligatorio, Entidad eps para clase de incapacidades 1   o 2(Enfermedad general-Licencia maternidad, paternidad)  o Entidad ARL para clase de incapacidad 3 o   4 (Accidente de trabajo-Enfermedad profesional).  De no ser llenada, se asuma la de el contrato.)</t>
-  </si>
-  <si>
-    <t>14698255</t>
-  </si>
-  <si>
-    <t>1007491493</t>
   </si>
 </sst>
 </file>
@@ -514,7 +508,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AB3"/>
+  <dimension ref="A1:AB1"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="24.109375" customWidth="1"/>
@@ -633,100 +627,6 @@
         <v>27</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A2">
-        <v>2</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>28</v>
-      </c>
-      <c r="F2">
-        <v>153</v>
-      </c>
-      <c r="G2">
-        <v>20260808</v>
-      </c>
-      <c r="H2">
-        <v>1</v>
-      </c>
-      <c r="I2">
-        <v>20260808</v>
-      </c>
-      <c r="J2">
-        <v>0</v>
-      </c>
-      <c r="L2">
-        <v>0</v>
-      </c>
-      <c r="S2">
-        <v>0</v>
-      </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
-      <c r="U2">
-        <v>0</v>
-      </c>
-      <c r="W2">
-        <v>0</v>
-      </c>
-      <c r="X2">
-        <v>0</v>
-      </c>
-      <c r="Y2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3">
-        <v>153</v>
-      </c>
-      <c r="G3">
-        <v>20260808</v>
-      </c>
-      <c r="H3">
-        <v>1</v>
-      </c>
-      <c r="I3">
-        <v>20260808</v>
-      </c>
-      <c r="J3">
-        <v>0</v>
-      </c>
-      <c r="L3">
-        <v>0</v>
-      </c>
-      <c r="S3">
-        <v>0</v>
-      </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
-      <c r="U3">
-        <v>0</v>
-      </c>
-      <c r="W3">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>0</v>
-      </c>
-      <c r="Y3">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
